--- a/diseases/d145/2010-2014.xlsx
+++ b/diseases/d145/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6269,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7014,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8652,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13418,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +15056,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +15801,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16316,6 +16546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17204,6 +17439,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17944,6 +18184,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +19077,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19572,6 +19822,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21052,6 +21312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21940,6 +22205,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22680,6 +22950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23420,6 +23695,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24308,6 +24588,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25048,6 +25333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26226,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26674,6 +26969,11 @@
       <c r="S177" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">

--- a/diseases/d145/2010-2014.xlsx
+++ b/diseases/d145/2010-2014.xlsx
@@ -5825,28 +5825,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5973,28 +5987,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6121,28 +6149,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6422,28 +6464,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6570,28 +6626,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6718,28 +6788,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6866,28 +6950,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -7167,28 +7265,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7315,28 +7427,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7463,28 +7589,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7611,28 +7751,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7759,28 +7913,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -8060,28 +8228,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8208,28 +8390,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8356,28 +8552,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8504,28 +8714,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8805,28 +9029,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8953,28 +9191,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9101,28 +9353,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9249,28 +9515,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9550,28 +9830,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9698,28 +9992,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9846,28 +10154,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -9994,28 +10316,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -10295,28 +10631,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -10443,28 +10793,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -10591,28 +10955,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -10739,28 +11117,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -10887,28 +11279,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -11188,28 +11594,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11336,28 +11756,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -11484,28 +11918,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -11632,28 +12080,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -11933,28 +12395,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -12081,28 +12557,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12229,28 +12719,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -12377,28 +12881,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -12525,28 +13043,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12826,28 +13358,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -12974,28 +13520,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -13122,28 +13682,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -13270,28 +13844,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -13571,28 +14159,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13719,28 +14321,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13867,28 +14483,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -14015,28 +14645,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -14316,28 +14960,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14464,28 +15122,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14612,28 +15284,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14760,28 +15446,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -14908,28 +15608,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -15209,28 +15923,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15357,28 +16085,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15505,28 +16247,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15653,28 +16409,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -15954,28 +16724,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -16102,28 +16886,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -16250,28 +17048,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -16398,28 +17210,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -16699,28 +17525,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -16847,28 +17687,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -16995,28 +17849,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -17143,28 +18011,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -17291,28 +18173,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -17592,28 +18488,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -17740,28 +18650,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -17888,28 +18812,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -18036,28 +18974,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -18337,28 +19289,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18485,28 +19451,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -18633,28 +19613,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -18781,28 +19775,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -18929,28 +19937,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -19230,28 +20252,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -19378,28 +20414,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -19526,28 +20576,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -19674,28 +20738,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -19975,28 +21053,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -20123,28 +21215,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -20271,28 +21377,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -20419,28 +21539,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -20720,28 +21854,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -20868,28 +22016,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -21016,28 +22178,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -21164,28 +22340,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -21465,28 +22655,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -21613,28 +22817,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -21761,28 +22979,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -21909,28 +23141,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -22057,28 +23303,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -22358,28 +23618,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -22506,28 +23780,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -22654,28 +23942,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -22802,28 +24104,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -23103,28 +24419,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -23251,28 +24581,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -23399,28 +24743,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -23547,28 +24905,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -23848,28 +25220,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -23996,28 +25382,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -24144,28 +25544,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -24292,28 +25706,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -24440,28 +25868,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -24741,28 +26183,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -24889,28 +26345,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -25037,28 +26507,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -25185,28 +26669,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -25486,28 +26984,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -25634,28 +27146,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -25782,28 +27308,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -25930,28 +27470,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -26078,28 +27632,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -26379,28 +27947,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -26527,28 +28109,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -26675,28 +28271,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -26823,28 +28433,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -27124,28 +28748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -27272,28 +28910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -27420,28 +29072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -27568,28 +29234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">

--- a/diseases/d145/2010-2014.xlsx
+++ b/diseases/d145/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4290,11 +3945,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4307,22 +3957,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4443,11 +4083,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4460,22 +4095,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4596,11 +4221,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4613,22 +4233,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4749,11 +4359,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4766,22 +4371,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4902,11 +4497,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4919,22 +4509,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5055,11 +4635,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5072,22 +4647,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5208,11 +4773,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5225,22 +4785,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5361,11 +4911,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5378,22 +4923,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5514,11 +5049,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5531,22 +5061,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5667,11 +5187,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5684,22 +5199,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6306,11 +5811,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6323,22 +5823,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -7107,11 +6597,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7124,22 +6609,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -8070,11 +7545,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8087,22 +7557,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8871,11 +8331,6 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8888,22 +8343,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9672,11 +9117,6 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9689,22 +9129,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -10473,11 +9903,6 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10490,22 +9915,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -11436,11 +10851,6 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11453,22 +10863,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -12237,11 +11637,6 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12254,22 +11649,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -13200,11 +12585,6 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13217,22 +12597,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -14001,11 +13371,6 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14018,22 +13383,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -14802,11 +14157,6 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14819,22 +14169,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15765,11 +15105,6 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15782,22 +15117,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -16566,11 +15891,6 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16583,22 +15903,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -17367,11 +16677,6 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17384,22 +16689,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -18330,11 +17625,6 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18347,22 +17637,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -19131,11 +18411,6 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19148,22 +18423,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -20094,11 +19359,6 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20111,22 +19371,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -20895,11 +20145,6 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20912,22 +20157,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -21696,11 +20931,6 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21713,22 +20943,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -22497,11 +21717,6 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22514,22 +21729,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -23460,11 +22665,6 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23477,22 +22677,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -24261,11 +23451,6 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24278,22 +23463,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -25062,11 +24237,6 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25079,22 +24249,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -26025,11 +25185,6 @@
       <c r="R161" t="n">
         <v>0</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26042,22 +25197,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -26826,11 +25971,6 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26843,22 +25983,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -27789,11 +26919,6 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27806,22 +26931,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -28590,11 +27705,6 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28607,22 +27717,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>

--- a/diseases/d145/2010-2014.xlsx
+++ b/diseases/d145/2010-2014.xlsx
@@ -5319,17 +5319,15 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -5337,7 +5335,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5347,12 +5345,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -5362,11 +5355,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5481,17 +5469,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -5499,7 +5485,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5509,12 +5495,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -5524,11 +5505,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5643,17 +5619,15 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -5661,7 +5635,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5671,12 +5645,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -5686,11 +5655,6 @@
       </c>
       <c r="AT37" t="n">
         <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5943,17 +5907,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -5961,7 +5923,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5971,12 +5933,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -5986,11 +5943,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6105,17 +6057,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -6123,7 +6073,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6133,12 +6083,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6148,11 +6093,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6267,17 +6207,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -6285,7 +6223,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6295,12 +6233,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -6310,11 +6243,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6429,17 +6357,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -6447,7 +6373,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6457,12 +6383,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -6472,11 +6393,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6729,17 +6645,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -6747,7 +6661,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6757,12 +6671,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -6772,11 +6681,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6891,17 +6795,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -6909,7 +6811,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6919,12 +6821,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -6934,11 +6831,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7053,17 +6945,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -7071,7 +6961,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7081,12 +6971,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -7096,11 +6981,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7215,17 +7095,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -7233,7 +7111,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7243,12 +7121,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -7258,11 +7131,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7377,17 +7245,15 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -7395,7 +7261,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7405,12 +7271,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -7420,11 +7281,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7677,17 +7533,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -7695,7 +7549,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7705,12 +7559,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -7720,11 +7569,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7839,17 +7683,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -7857,7 +7699,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -7867,12 +7709,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -7882,11 +7719,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8001,17 +7833,15 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0.0007816879589998411</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -8019,7 +7849,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8029,12 +7859,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -8044,11 +7869,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8163,17 +7983,15 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -8181,7 +7999,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8191,12 +8009,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -8206,11 +8019,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8463,17 +8271,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -8481,7 +8287,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8491,12 +8297,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -8506,11 +8307,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8625,17 +8421,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -8643,7 +8437,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8653,12 +8447,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -8668,11 +8457,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8787,17 +8571,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -8805,7 +8587,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8815,12 +8597,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -8830,11 +8607,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8949,17 +8721,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -8967,7 +8737,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -8977,12 +8747,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -8992,11 +8757,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9249,17 +9009,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -9267,7 +9025,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9277,12 +9035,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -9292,11 +9045,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9411,17 +9159,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -9429,7 +9175,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9439,12 +9185,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -9454,11 +9195,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9573,17 +9309,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -9591,7 +9325,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9601,12 +9335,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -9616,11 +9345,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9735,17 +9459,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -9753,7 +9475,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9763,12 +9485,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -9778,11 +9495,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10035,17 +9747,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -10053,7 +9763,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10063,12 +9773,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -10078,11 +9783,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10197,17 +9897,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -10215,7 +9913,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10225,12 +9923,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -10240,11 +9933,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10359,17 +10047,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -10377,7 +10063,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10387,12 +10073,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -10402,11 +10083,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10521,17 +10197,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -10539,7 +10213,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10549,12 +10223,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -10564,11 +10233,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10683,17 +10347,15 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -10701,7 +10363,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -10711,12 +10373,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -10726,11 +10383,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10983,17 +10635,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -11001,7 +10651,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11011,12 +10661,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -11026,11 +10671,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11145,17 +10785,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -11163,7 +10801,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11173,12 +10811,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -11188,11 +10821,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11307,17 +10935,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -11325,7 +10951,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11335,12 +10961,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -11350,11 +10971,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11469,17 +11085,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -11487,7 +11101,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11497,12 +11111,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -11512,11 +11121,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11769,17 +11373,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -11787,7 +11389,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11797,12 +11399,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -11812,11 +11409,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11931,17 +11523,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -11949,7 +11539,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -11959,12 +11549,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -11974,11 +11559,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12093,17 +11673,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -12111,7 +11689,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12121,12 +11699,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -12136,11 +11709,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12255,17 +11823,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -12273,7 +11839,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -12283,12 +11849,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -12298,11 +11859,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12417,17 +11973,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -12435,7 +11989,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12445,12 +11999,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -12460,11 +12009,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12717,17 +12261,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -12735,7 +12277,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12745,12 +12287,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -12760,11 +12297,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12879,17 +12411,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -12897,7 +12427,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -12907,12 +12437,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -12922,11 +12447,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13041,17 +12561,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -13059,7 +12577,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13069,12 +12587,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -13084,11 +12597,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13203,17 +12711,15 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -13221,7 +12727,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13231,12 +12737,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -13246,11 +12747,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13503,17 +12999,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -13521,7 +13015,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13531,12 +13025,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -13546,11 +13035,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13665,17 +13149,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -13683,7 +13165,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13693,12 +13175,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -13708,11 +13185,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13827,17 +13299,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -13845,7 +13315,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13855,12 +13325,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -13870,11 +13335,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13989,17 +13449,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -14007,7 +13465,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14017,12 +13475,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -14032,11 +13485,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14289,17 +13737,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -14307,7 +13753,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14317,12 +13763,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -14332,11 +13773,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14451,17 +13887,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -14469,7 +13903,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -14479,12 +13913,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -14494,11 +13923,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14613,17 +14037,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -14631,7 +14053,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -14641,12 +14063,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -14656,11 +14073,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14775,17 +14187,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -14793,7 +14203,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -14803,12 +14213,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -14818,11 +14223,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14937,17 +14337,15 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -14955,7 +14353,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -14965,12 +14363,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -14980,11 +14373,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15237,17 +14625,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -15255,7 +14641,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -15265,12 +14651,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -15280,11 +14661,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15399,17 +14775,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -15417,7 +14791,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -15427,12 +14801,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -15442,11 +14811,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15561,17 +14925,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -15579,7 +14941,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -15589,12 +14951,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -15604,11 +14961,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15723,17 +15075,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -15741,7 +15091,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -15751,12 +15101,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -15766,11 +15111,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -16023,17 +15363,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -16041,7 +15379,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16051,12 +15389,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -16066,11 +15399,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16185,17 +15513,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -16203,7 +15529,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16213,12 +15539,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -16228,11 +15549,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16347,17 +15663,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -16365,7 +15679,7 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -16375,12 +15689,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
@@ -16390,11 +15699,6 @@
       </c>
       <c r="AT105" t="n">
         <v>1</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16509,17 +15813,15 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -16527,7 +15829,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -16537,12 +15839,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -16552,11 +15849,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -16809,17 +16101,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -16827,7 +16117,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -16837,12 +16127,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -16852,11 +16137,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16971,17 +16251,15 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -16989,7 +16267,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -16999,12 +16277,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -17014,11 +16287,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17133,17 +16401,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -17151,7 +16417,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -17161,12 +16427,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -17176,11 +16437,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17295,17 +16551,15 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -17313,7 +16567,7 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -17323,12 +16577,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -17338,11 +16587,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17457,17 +16701,15 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -17475,7 +16717,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -17485,12 +16727,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -17500,11 +16737,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17757,17 +16989,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -17775,7 +17005,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -17785,12 +17015,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -17800,11 +17025,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -17919,17 +17139,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -17937,7 +17155,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -17947,12 +17165,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -17962,11 +17175,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18081,17 +17289,15 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -18099,7 +17305,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -18109,12 +17315,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -18124,11 +17325,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18243,17 +17439,15 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -18261,7 +17455,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -18271,12 +17465,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -18286,11 +17475,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18543,17 +17727,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -18561,7 +17743,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -18571,12 +17753,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -18586,11 +17763,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18705,17 +17877,15 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -18723,7 +17893,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18733,12 +17903,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -18748,11 +17913,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18867,17 +18027,15 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -18885,7 +18043,7 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -18895,12 +18053,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
@@ -18910,11 +18063,6 @@
       </c>
       <c r="AT121" t="n">
         <v>1</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19029,17 +18177,15 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -19047,7 +18193,7 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19057,12 +18203,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
@@ -19072,11 +18213,6 @@
       </c>
       <c r="AT122" t="n">
         <v>1</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19191,17 +18327,15 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -19209,7 +18343,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -19219,12 +18353,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -19234,11 +18363,6 @@
       </c>
       <c r="AT123" t="n">
         <v>1</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19491,17 +18615,15 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -19509,7 +18631,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -19519,12 +18641,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -19534,11 +18651,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -19653,17 +18765,15 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U126" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -19671,7 +18781,7 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -19681,12 +18791,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
@@ -19696,11 +18801,6 @@
       </c>
       <c r="AT126" t="n">
         <v>1</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19815,17 +18915,15 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -19833,7 +18931,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -19843,12 +18941,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
@@ -19858,11 +18951,6 @@
       </c>
       <c r="AT127" t="n">
         <v>1</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -19977,17 +19065,15 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U128" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -19995,7 +19081,7 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -20005,12 +19091,7 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
@@ -20020,11 +19101,6 @@
       </c>
       <c r="AT128" t="n">
         <v>1</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20277,17 +19353,15 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -20295,7 +19369,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -20305,12 +19379,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -20320,11 +19389,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20439,17 +19503,15 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -20457,7 +19519,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -20467,12 +19529,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -20482,11 +19539,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20601,17 +19653,15 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -20619,7 +19669,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -20629,12 +19679,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -20644,11 +19689,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -20763,17 +19803,15 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U133" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -20781,7 +19819,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -20791,12 +19829,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
@@ -20806,11 +19839,6 @@
       </c>
       <c r="AT133" t="n">
         <v>1</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -21063,17 +20091,15 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -21081,7 +20107,7 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21091,12 +20117,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr">
@@ -21106,11 +20127,6 @@
       </c>
       <c r="AT135" t="n">
         <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21225,17 +20241,15 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U136" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -21243,7 +20257,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -21253,12 +20267,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
@@ -21268,11 +20277,6 @@
       </c>
       <c r="AT136" t="n">
         <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21387,17 +20391,15 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -21405,7 +20407,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -21415,12 +20417,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -21430,11 +20427,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21549,17 +20541,15 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -21567,7 +20557,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -21577,12 +20567,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -21592,11 +20577,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21849,17 +20829,15 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -21867,7 +20845,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -21877,12 +20855,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
@@ -21892,11 +20865,6 @@
       </c>
       <c r="AT140" t="n">
         <v>1</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -22011,17 +20979,15 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -22029,7 +20995,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -22039,12 +21005,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
@@ -22054,11 +21015,6 @@
       </c>
       <c r="AT141" t="n">
         <v>1</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22173,17 +21129,15 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
       <c r="Q142" t="n">
         <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -22191,7 +21145,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -22201,12 +21155,7 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
@@ -22216,11 +21165,6 @@
       </c>
       <c r="AT142" t="n">
         <v>1</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22335,17 +21279,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -22353,7 +21295,7 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -22363,12 +21305,7 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
@@ -22378,11 +21315,6 @@
       </c>
       <c r="AT143" t="n">
         <v>1</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22497,17 +21429,15 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -22515,7 +21445,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -22525,12 +21455,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
@@ -22540,11 +21465,6 @@
       </c>
       <c r="AT144" t="n">
         <v>1</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22797,17 +21717,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -22815,7 +21733,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -22825,12 +21743,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -22840,11 +21753,6 @@
       </c>
       <c r="AT146" t="n">
         <v>1</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -22959,17 +21867,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -22977,7 +21883,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -22987,12 +21893,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -23002,11 +21903,6 @@
       </c>
       <c r="AT147" t="n">
         <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -23121,17 +22017,15 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -23139,7 +22033,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -23149,12 +22043,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
@@ -23164,11 +22053,6 @@
       </c>
       <c r="AT148" t="n">
         <v>1</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23283,17 +22167,15 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -23301,7 +22183,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -23311,12 +22193,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
@@ -23326,11 +22203,6 @@
       </c>
       <c r="AT149" t="n">
         <v>1</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23583,17 +22455,15 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -23601,7 +22471,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -23611,12 +22481,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -23626,11 +22491,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -23745,17 +22605,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -23763,7 +22621,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -23773,12 +22631,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -23788,11 +22641,6 @@
       </c>
       <c r="AT152" t="n">
         <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -23907,17 +22755,15 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -23925,7 +22771,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -23935,12 +22781,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
@@ -23950,11 +22791,6 @@
       </c>
       <c r="AT153" t="n">
         <v>1</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -24069,17 +22905,15 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -24087,7 +22921,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -24097,12 +22931,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -24112,11 +22941,6 @@
       </c>
       <c r="AT154" t="n">
         <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24369,17 +23193,15 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -24387,7 +23209,7 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -24397,12 +23219,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
@@ -24412,11 +23229,6 @@
       </c>
       <c r="AT156" t="n">
         <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24531,17 +23343,15 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -24549,7 +23359,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -24559,12 +23369,7 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
@@ -24574,11 +23379,6 @@
       </c>
       <c r="AT157" t="n">
         <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24693,17 +23493,15 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -24711,7 +23509,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -24721,12 +23519,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -24736,11 +23529,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -24855,17 +23643,15 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -24873,7 +23659,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -24883,12 +23669,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -24898,11 +23679,6 @@
       </c>
       <c r="AT159" t="n">
         <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -25017,17 +23793,15 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -25035,7 +23809,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -25045,12 +23819,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
@@ -25060,11 +23829,6 @@
       </c>
       <c r="AT160" t="n">
         <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25317,17 +24081,15 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -25335,7 +24097,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -25345,12 +24107,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -25360,11 +24117,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25479,17 +24231,15 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U163" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -25497,7 +24247,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -25507,12 +24257,7 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
@@ -25522,11 +24267,6 @@
       </c>
       <c r="AT163" t="n">
         <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25641,17 +24381,15 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
       <c r="Q164" t="n">
         <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U164" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -25659,7 +24397,7 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -25669,12 +24407,7 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
@@ -25684,11 +24417,6 @@
       </c>
       <c r="AT164" t="n">
         <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25803,17 +24531,15 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U165" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -25821,7 +24547,7 @@
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -25831,12 +24557,7 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
@@ -25846,11 +24567,6 @@
       </c>
       <c r="AT165" t="n">
         <v>1</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -26103,17 +24819,15 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -26121,7 +24835,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -26131,12 +24845,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -26146,11 +24855,6 @@
       </c>
       <c r="AT167" t="n">
         <v>1</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -26265,17 +24969,15 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -26283,7 +24985,7 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -26293,12 +24995,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
@@ -26308,11 +25005,6 @@
       </c>
       <c r="AT168" t="n">
         <v>1</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26427,17 +25119,15 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -26445,7 +25135,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -26455,12 +25145,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -26470,11 +25155,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26589,17 +25269,15 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -26607,7 +25285,7 @@
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -26617,12 +25295,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
@@ -26632,11 +25305,6 @@
       </c>
       <c r="AT170" t="n">
         <v>1</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26751,17 +25419,15 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -26769,7 +25435,7 @@
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -26779,12 +25445,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
@@ -26794,11 +25455,6 @@
       </c>
       <c r="AT171" t="n">
         <v>1</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -27051,17 +25707,15 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -27069,7 +25723,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -27079,12 +25733,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
@@ -27094,11 +25743,6 @@
       </c>
       <c r="AT173" t="n">
         <v>1</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -27213,17 +25857,15 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -27231,7 +25873,7 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -27241,12 +25883,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
@@ -27256,11 +25893,6 @@
       </c>
       <c r="AT174" t="n">
         <v>1</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -27375,17 +26007,15 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -27393,7 +26023,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -27403,12 +26033,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -27418,11 +26043,6 @@
       </c>
       <c r="AT175" t="n">
         <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -27537,17 +26157,15 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -27555,7 +26173,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -27565,12 +26183,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
@@ -27580,11 +26193,6 @@
       </c>
       <c r="AT176" t="n">
         <v>1</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -27837,17 +26445,15 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -27855,7 +26461,7 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -27865,12 +26471,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
@@ -27880,11 +26481,6 @@
       </c>
       <c r="AT178" t="n">
         <v>1</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -27999,17 +26595,15 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -28017,7 +26611,7 @@
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -28027,12 +26621,7 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
@@ -28042,11 +26631,6 @@
       </c>
       <c r="AT179" t="n">
         <v>1</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -28161,17 +26745,15 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -28179,7 +26761,7 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -28189,12 +26771,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
@@ -28204,11 +26781,6 @@
       </c>
       <c r="AT180" t="n">
         <v>1</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -28323,17 +26895,15 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>HOLD_JP_f98a3c6295c7b36bb3af36bb605d</t>
@@ -28341,7 +26911,7 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -28351,12 +26921,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
@@ -28366,11 +26931,6 @@
       </c>
       <c r="AT181" t="n">
         <v>1</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>

--- a/diseases/d145/2010-2014.xlsx
+++ b/diseases/d145/2010-2014.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,12 +941,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1047,6 +1077,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,12 +1094,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1185,6 +1230,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,12 +1247,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1323,6 +1383,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1335,12 +1400,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1461,6 +1536,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,12 +1553,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1599,6 +1689,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1611,12 +1706,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1737,6 +1842,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,12 +1859,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1875,6 +1995,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,12 +2012,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2013,6 +2148,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,12 +2165,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2151,6 +2301,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,12 +2318,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2289,6 +2454,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,12 +2471,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2427,6 +2607,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2439,12 +2624,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2565,6 +2760,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,12 +2777,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2703,6 +2913,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2715,12 +2930,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2841,6 +3066,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2853,12 +3083,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2979,6 +3219,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2991,12 +3236,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3117,6 +3372,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3129,12 +3389,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3255,6 +3525,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3267,12 +3542,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3393,6 +3678,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3405,12 +3695,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3531,6 +3831,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3543,12 +3848,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3669,6 +3984,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3681,12 +4001,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3807,6 +4137,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3819,12 +4154,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3945,6 +4290,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3957,12 +4307,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4083,6 +4443,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4095,12 +4460,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4221,6 +4596,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4233,12 +4613,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4359,6 +4749,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4371,12 +4766,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4497,6 +4902,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4509,12 +4919,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4635,6 +5055,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4647,12 +5072,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4773,6 +5208,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4785,12 +5225,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4911,6 +5361,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4923,12 +5378,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5049,6 +5514,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5061,12 +5531,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5187,6 +5667,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5199,12 +5684,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5775,6 +6270,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5787,12 +6287,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6513,6 +7023,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6525,12 +7040,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7401,6 +7926,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7413,12 +7943,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8139,6 +8679,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8151,12 +8696,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8877,6 +9432,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8889,12 +9449,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9615,6 +10185,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9627,12 +10202,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10503,6 +11088,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10515,12 +11105,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11241,6 +11841,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11253,12 +11858,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12129,6 +12744,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12141,12 +12761,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12867,6 +13497,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12879,12 +13514,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13605,6 +14250,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13617,12 +14267,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14493,6 +15153,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14505,12 +15170,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15231,6 +15906,11 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15243,12 +15923,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15969,6 +16659,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15981,12 +16676,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16857,6 +17562,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16869,12 +17579,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -17595,6 +18315,11 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17607,12 +18332,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18483,6 +19218,11 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18495,12 +19235,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19221,6 +19971,11 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19233,12 +19988,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -19959,6 +20724,11 @@
       <c r="R134" t="n">
         <v>0</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19971,12 +20741,22 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -20697,6 +21477,11 @@
       <c r="R139" t="n">
         <v>0</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20709,12 +21494,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -21585,6 +22380,11 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21597,12 +22397,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -22323,6 +23133,11 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22335,12 +23150,22 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23061,6 +23886,11 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23073,12 +23903,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -23949,6 +24789,11 @@
       <c r="R161" t="n">
         <v>0</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23961,12 +24806,22 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -24687,6 +25542,11 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24699,12 +25559,22 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -25575,6 +26445,11 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25587,12 +26462,22 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -26313,6 +27198,11 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26325,12 +27215,22 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
